--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_306_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_306_R31.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5709</v>
+        <v>4.9728</v>
       </c>
       <c r="E2" t="n">
-        <v>1.936</v>
+        <v>1.7748</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6349</v>
+        <v>3.198</v>
       </c>
       <c r="G2" t="n">
         <v>2.0361</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5169</v>
+        <v>0.9188</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3541</v>
+        <v>0.1928</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1628</v>
+        <v>0.726</v>
       </c>
       <c r="V2" t="n">
         <v>0.3943</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3812</v>
+        <v>4.2542</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7455</v>
+        <v>2.8202</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6356</v>
+        <v>1.434</v>
       </c>
       <c r="G3" t="n">
         <v>3.4543</v>
@@ -688,13 +688,13 @@
         <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>0.463</v>
+        <v>0.3361</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3655</v>
+        <v>-0.2908</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8285</v>
+        <v>0.6269</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3185</v>
+        <v>2.0211</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1263</v>
+        <v>4.8288</v>
       </c>
       <c r="F4" t="n">
         <v>-2.8078</v>
@@ -766,10 +766,10 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6553</v>
+        <v>0.3578</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8521</v>
+        <v>0.5546</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1968</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3702</v>
+        <v>1.2198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0743</v>
+        <v>0.8567</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2958</v>
+        <v>0.3631</v>
       </c>
       <c r="G5" t="n">
         <v>0.738</v>
@@ -844,13 +844,13 @@
         <v>2.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9735</v>
+        <v>-0.1239</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8804</v>
+        <v>-0.098</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0931</v>
+        <v>-0.0259</v>
       </c>
       <c r="V5" t="n">
         <v>0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1665</v>
+        <v>0.1739</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1465</v>
+        <v>-1.0718</v>
       </c>
       <c r="F6" t="n">
-        <v>1.313</v>
+        <v>1.2458</v>
       </c>
       <c r="G6" t="n">
         <v>-2.8684</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4112</v>
+        <v>0.4187</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2794</v>
+        <v>0.3541</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1318</v>
+        <v>0.0646</v>
       </c>
       <c r="V6" t="n">
         <v>0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5225</v>
+        <v>-1.1606</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6254</v>
+        <v>-0.9609</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1028</v>
+        <v>-0.1996</v>
       </c>
       <c r="G7" t="n">
         <v>-3.949</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6304</v>
+        <v>-0.2684</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8804</v>
+        <v>-0.2159</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>-0.0525</v>
       </c>
       <c r="V7" t="n">
         <v>3.7527</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2526</v>
+        <v>-1.3124</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8136</v>
+        <v>-1.3104</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.439</v>
+        <v>-0.0021</v>
       </c>
       <c r="G8" t="n">
         <v>1.0536</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.234</v>
+        <v>-0.2939</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1123</v>
+        <v>-0.6091</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1217</v>
+        <v>0.3152</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6083</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8818</v>
+        <v>-3.3584</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3737</v>
+        <v>-4.8732</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5081</v>
+        <v>1.5148</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9833</v>
+        <v>-1.6424</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1427</v>
+        <v>-2.2113</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.1261</v>
+        <v>0.5689</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8212</v>
+        <v>-2.318</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2505</v>
+        <v>-2.9437</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.0718</v>
+        <v>0.6257</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1621</v>
+        <v>0.6757</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1078</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0543</v>
+        <v>-0.0568</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9212</v>
+        <v>0.0314</v>
       </c>
       <c r="T9" t="n">
-        <v>0.767</v>
+        <v>-0.2357</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1542</v>
+        <v>0.2671</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8197</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3994</v>
+        <v>-4.3125</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3764</v>
+        <v>-3.7708</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9771</v>
+        <v>-0.5417</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6424</v>
+        <v>-3.9833</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2113</v>
+        <v>1.1427</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5689</v>
+        <v>-5.1261</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.318</v>
+        <v>-1.8212</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.9437</v>
+        <v>1.2505</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6257</v>
+        <v>-3.0718</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6757</v>
+        <v>-2.1621</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7324000000000001</v>
+        <v>-0.1078</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0568</v>
+        <v>-2.0543</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0095</v>
+        <v>0.4905</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7389</v>
+        <v>0.3699</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2706</v>
+        <v>0.1206</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8197</v>
@@ -1267,25 +1267,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.750999999999999</v>
+        <v>2.4979</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.453500000000002</v>
+        <v>-1.7066</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2043</v>
+        <v>4.2045</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.371400000000001</v>
+        <v>-4.3714</v>
       </c>
       <c r="H11" t="n">
-        <v>9.2964</v>
+        <v>9.296399999999998</v>
       </c>
       <c r="I11" t="n">
         <v>-13.6681</v>
       </c>
       <c r="J11" t="n">
-        <v>4.312000000000001</v>
+        <v>4.312</v>
       </c>
       <c r="K11" t="n">
         <v>10.0513</v>
@@ -1294,16 +1294,16 @@
         <v>-5.7394</v>
       </c>
       <c r="M11" t="n">
-        <v>-8.683299999999999</v>
+        <v>-8.683300000000001</v>
       </c>
       <c r="N11" t="n">
         <v>-0.7546999999999998</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.9288</v>
+        <v>-7.928799999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>4.639100000000001</v>
+        <v>4.6391</v>
       </c>
       <c r="Q11" t="n">
         <v>-12.7573</v>
@@ -1312,13 +1312,13 @@
         <v>17.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1202</v>
+        <v>1.8671</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7248999999999999</v>
+        <v>0.02190000000000003</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8451</v>
+        <v>1.8452</v>
       </c>
       <c r="V11" t="n">
         <v>0.3632000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.4523</v>
+        <v>6.0332</v>
       </c>
       <c r="E12" t="n">
-        <v>6.6329</v>
+        <v>5.5713</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8194</v>
+        <v>0.4618</v>
       </c>
       <c r="G12" t="n">
         <v>2.4115</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>2.685</v>
+        <v>1.2658</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5454</v>
+        <v>0.4839</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1396</v>
+        <v>0.782</v>
       </c>
       <c r="V12" t="n">
         <v>1.8919</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1681</v>
+        <v>2.2494</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0474</v>
+        <v>0.2062</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1208</v>
+        <v>2.0432</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6888</v>
+        <v>2.6784</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2845</v>
+        <v>-2.1932</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5957</v>
+        <v>4.8716</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6959</v>
+        <v>2.8433</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7695</v>
+        <v>-0.9306</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0736</v>
+        <v>3.774</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0071</v>
+        <v>-0.165</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5149</v>
+        <v>-1.2626</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5221</v>
+        <v>1.0976</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9291</v>
+        <v>0.2153</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9752</v>
+        <v>-0.1373</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0461</v>
+        <v>0.3525</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1428</v>
+        <v>1.7012</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6194</v>
+        <v>1.2031</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7622</v>
+        <v>0.4981</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6784</v>
+        <v>3.3414</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.1932</v>
+        <v>0.0155</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8716</v>
+        <v>3.3259</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8433</v>
+        <v>3.3923</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9306</v>
+        <v>1.3213</v>
       </c>
       <c r="L14" t="n">
-        <v>3.774</v>
+        <v>2.071</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.165</v>
+        <v>-0.0508</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2626</v>
+        <v>-1.3057</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0976</v>
+        <v>1.2549</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7834</v>
+        <v>-1.6237</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8913</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.963</v>
+        <v>-0.7073</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0716</v>
+        <v>0.1393</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2836</v>
+        <v>-1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2836</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0506</v>
+        <v>0.4661</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2031</v>
+        <v>-0.7783</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1525</v>
+        <v>1.2444</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3414</v>
+        <v>-0.6888</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0155</v>
+        <v>-1.2845</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3259</v>
+        <v>0.5957</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3923</v>
+        <v>-0.6959</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3213</v>
+        <v>-0.7695</v>
       </c>
       <c r="L15" t="n">
-        <v>2.071</v>
+        <v>0.0736</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0508</v>
+        <v>0.0071</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3057</v>
+        <v>-0.5149</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2549</v>
+        <v>0.5221</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2186</v>
+        <v>0.2271</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7073</v>
+        <v>0.1496</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5113</v>
+        <v>0.0775</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3151</v>
+        <v>0.1357</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9765</v>
+        <v>-1.2125</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2917</v>
+        <v>1.3481</v>
       </c>
       <c r="G16" t="n">
         <v>0.0728</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3299</v>
+        <v>0.1505</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1098</v>
+        <v>-0.3457</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4397</v>
+        <v>0.4962</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5248</v>
+        <v>0.1184</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3398</v>
+        <v>-1.426</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1851</v>
+        <v>1.5444</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6601</v>
+        <v>-1.31</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8174</v>
+        <v>-1.4405</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1573</v>
+        <v>0.1305</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0336</v>
+        <v>-0.4624</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0336</v>
+        <v>-0.1779</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.2845</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6938</v>
+        <v>-0.8476</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.851</v>
+        <v>-1.2626</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>0.415</v>
       </c>
       <c r="P17" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3286</v>
+        <v>-0.2495</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3734</v>
+        <v>-0.554</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0448</v>
+        <v>0.3044</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.606</v>
+        <v>-0.3651</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5421</v>
+        <v>-0.6601</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0639</v>
+        <v>0.295</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5993000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3154</v>
+        <v>0.5564</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4955</v>
+        <v>0.3776</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1801</v>
+        <v>0.1788</v>
       </c>
       <c r="V18" t="n">
         <v>0.1418</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9711</v>
+        <v>-0.4576</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1337</v>
+        <v>-0.3398</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1627</v>
+        <v>-0.1178</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.31</v>
+        <v>-0.6601</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4405</v>
+        <v>-0.8174</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1305</v>
+        <v>0.1573</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4624</v>
+        <v>0.0336</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1779</v>
+        <v>0.0336</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2845</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8476</v>
+        <v>-0.6938</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2626</v>
+        <v>-0.851</v>
       </c>
       <c r="O19" t="n">
-        <v>0.415</v>
+        <v>0.1573</v>
       </c>
       <c r="P19" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.339</v>
+        <v>-0.2614</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2617</v>
+        <v>-0.3734</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.112</v>
       </c>
       <c r="V19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7137</v>
+        <v>-2.0681</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4631</v>
+        <v>-1.1092</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2506</v>
+        <v>-0.9589</v>
       </c>
       <c r="G20" t="n">
         <v>2.7561</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6141</v>
+        <v>0.0314</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0914</v>
+        <v>0.2003</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4648</v>
+        <v>-2.8979</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8827</v>
+        <v>-2.7647</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5821</v>
+        <v>-0.1332</v>
       </c>
       <c r="G21" t="n">
         <v>-0.32</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.449</v>
+        <v>0.118</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1019</v>
+        <v>0.016</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.347</v>
+        <v>0.1019</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5997</v>
+        <v>-4.3073</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6666</v>
+        <v>-3.4307</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9331</v>
+        <v>-0.8766</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3106</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.539</v>
+        <v>-0.2467</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8215</v>
+        <v>-0.5856</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2825</v>
+        <v>0.3389</v>
       </c>
       <c r="V22" t="n">
         <v>-1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.751199999999999</v>
+        <v>0.6080000000000005</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7405</v>
+        <v>-4.740699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>2.9895</v>
+        <v>5.3485</v>
       </c>
       <c r="G23" t="n">
         <v>4.371399999999999</v>
@@ -2221,7 +2221,7 @@
         <v>13.6681</v>
       </c>
       <c r="J23" t="n">
-        <v>8.683399999999999</v>
+        <v>8.683400000000002</v>
       </c>
       <c r="K23" t="n">
         <v>0.7547000000000001</v>
@@ -2236,7 +2236,7 @@
         <v>-10.0512</v>
       </c>
       <c r="O23" t="n">
-        <v>5.7393</v>
+        <v>5.739299999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-4.6391</v>
@@ -2248,13 +2248,13 @@
         <v>12.7575</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1202</v>
+        <v>1.2389</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.8453</v>
+        <v>-1.8451</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7249999999999999</v>
+        <v>3.0838</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3632000000000002</v>
